--- a/education_surveys/033_teacher_favorite_things_form--education_surveys.xlsx
+++ b/education_surveys/033_teacher_favorite_things_form--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Favorite Subject</t>
+          <t>Favorite Subject (2)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>favorite_food</t>
+          <t>favorite_food_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Favorite Food</t>
+          <t>Favorite Food 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>favorite_band</t>
+          <t>favorite_band_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Favorite Music</t>
+          <t>Page 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Favorite Music</t>
+          <t>Favorite Music (3)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>favorite_game</t>
+          <t>favorite_game_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Favorite Game</t>
+          <t>Favorite Game 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>favorite_food_choices</t>
+          <t>favorite_food_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1302,7 +1302,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>favorite_food_choices</t>
+          <t>favorite_food_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1353,7 +1353,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>favorite_game_choices</t>
+          <t>favorite_game_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1370,7 +1370,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>favorite_game_choices</t>
+          <t>favorite_game_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
